--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484748_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484748_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4425</v>
+        <v>4.9839</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5419</v>
+        <v>4.9774</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0993</v>
+        <v>0.0065</v>
       </c>
       <c r="G2" t="n">
         <v>2.462</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6788</v>
+        <v>1.2202</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6235</v>
+        <v>1.0591</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0553</v>
+        <v>0.1611</v>
       </c>
       <c r="V2" t="n">
         <v>1.8678</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5233</v>
+        <v>0.9529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.3066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5934</v>
+        <v>0.6463</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4019</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9817</v>
+        <v>0.4113</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.2644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0941</v>
+        <v>0.147</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9563</v>
+        <v>0.4725</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7342</v>
+        <v>-1.0064</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6906</v>
+        <v>1.4789</v>
       </c>
       <c r="G4" t="n">
         <v>-2.0298</v>
@@ -766,13 +766,13 @@
         <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>1.854</v>
+        <v>1.3702</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2556</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5985</v>
+        <v>0.3868</v>
       </c>
       <c r="V4" t="n">
         <v>0.9434</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3009</v>
+        <v>0.3273</v>
       </c>
       <c r="E5" t="n">
         <v>1.4663</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1655</v>
+        <v>-1.139</v>
       </c>
       <c r="G5" t="n">
         <v>0.3004</v>
@@ -844,13 +844,13 @@
         <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4908</v>
+        <v>0.5173</v>
       </c>
       <c r="T5" t="n">
         <v>0.4732</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2452</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6599</v>
+        <v>-0.2744</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4453</v>
+        <v>-0.1127</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2146</v>
+        <v>-0.1617</v>
       </c>
       <c r="G6" t="n">
         <v>-2.5264</v>
@@ -922,13 +922,13 @@
         <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9229000000000001</v>
+        <v>1.3084</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7512</v>
+        <v>1.0837</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1717</v>
+        <v>0.2246</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9434</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3212</v>
+        <v>-0.8026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3931</v>
+        <v>0.9206</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7143</v>
+        <v>-1.7231</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8846000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2616</v>
+        <v>0.7802</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1604</v>
+        <v>0.6878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1012</v>
+        <v>0.0924</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3208</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7793</v>
+        <v>-1.9957</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0488</v>
+        <v>-3.4239</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2695</v>
+        <v>1.4282</v>
       </c>
       <c r="G8" t="n">
         <v>-3.547</v>
@@ -1078,13 +1078,13 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3645</v>
+        <v>0.4191</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3128</v>
+        <v>0.3121</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0517</v>
+        <v>0.1071</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0426</v>
+        <v>-2.0241</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.663</v>
+        <v>-1.5123</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3796</v>
+        <v>-0.5118</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8787</v>
@@ -1156,13 +1156,13 @@
         <v>2.6418</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0882</v>
+        <v>0.9303</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3716</v>
+        <v>0.7791</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2834</v>
+        <v>0.1512</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4199999999999982</v>
+        <v>1.6398</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4398999999999997</v>
+        <v>1.615600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01979999999999982</v>
+        <v>0.02429999999999988</v>
       </c>
       <c r="G10" t="n">
         <v>-7.506</v>
@@ -1234,13 +1234,13 @@
         <v>16.0395</v>
       </c>
       <c r="S10" t="n">
-        <v>5.7371</v>
+        <v>6.957</v>
       </c>
       <c r="T10" t="n">
-        <v>4.4671</v>
+        <v>5.6428</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2701</v>
+        <v>1.3143</v>
       </c>
       <c r="V10" t="n">
         <v>0.3017999999999998</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.1261</v>
+        <v>5.2615</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1079</v>
+        <v>2.6207</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0182</v>
+        <v>2.6408</v>
       </c>
       <c r="G11" t="n">
         <v>5.7558</v>
@@ -1312,13 +1312,13 @@
         <v>2.0757</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3327</v>
+        <v>0.4681</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3585</v>
+        <v>-0.1286</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9742</v>
+        <v>0.5968</v>
       </c>
       <c r="V11" t="n">
         <v>-0.019</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1163</v>
+        <v>3.2138</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1255</v>
+        <v>1.8332</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9908</v>
+        <v>1.3806</v>
       </c>
       <c r="G12" t="n">
         <v>1.1051</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0835</v>
+        <v>0.014</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3585</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.442</v>
+        <v>-0.0522</v>
       </c>
       <c r="V12" t="n">
         <v>0.019</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. TAEÑO ELEZ</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5848</v>
+        <v>2.4925</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5848</v>
+        <v>2.9415</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.449</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5848</v>
+        <v>2.9861</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5848</v>
+        <v>2.0355</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.9505</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5848</v>
+        <v>3.8744</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5848</v>
+        <v>1.9072</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.9672</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.8883</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.1284</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-1.0167</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1.1351</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.1023</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1.0328</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>M. TAEÑO ELEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9001</v>
+        <v>1.5848</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1621</v>
+        <v>1.5848</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.262</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9861</v>
+        <v>1.5848</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0355</v>
+        <v>1.5848</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9505</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8744</v>
+        <v>1.5848</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9072</v>
+        <v>1.5848</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9672</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8883</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1284</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0167</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7276</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8818</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.8458</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4761</v>
+        <v>-0.4232</v>
       </c>
       <c r="E15" t="n">
         <v>-0.726</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2499</v>
+        <v>0.3028</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5114</v>
@@ -1624,13 +1624,13 @@
         <v>0.1887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1534</v>
+        <v>-0.1005</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0359</v>
+        <v>0.0171</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0395</v>
+        <v>-1.387</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1038</v>
+        <v>-1.3961</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0643</v>
+        <v>0.0091</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3255</v>
@@ -1702,13 +1702,13 @@
         <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2293</v>
+        <v>-0.1183</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>-0.2306</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1676</v>
+        <v>0.1123</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8527</v>
+        <v>-1.7289</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0636</v>
+        <v>0.0339</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7892</v>
+        <v>-1.7627</v>
       </c>
       <c r="G17" t="n">
         <v>0.483</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.7214</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5291</v>
+        <v>-0.4317</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3162</v>
+        <v>-0.2898</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8678</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.965</v>
+        <v>-1.7484</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5178</v>
+        <v>-1.5155</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4472</v>
+        <v>-0.2329</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9325</v>
+        <v>0.0835</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1902</v>
+        <v>-1.1183</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7423</v>
+        <v>1.2018</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1289</v>
+        <v>0.9718</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0055</v>
+        <v>-0.9869</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1234</v>
+        <v>1.9587</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0614</v>
+        <v>-0.8883</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1956</v>
+        <v>-0.1315</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8657</v>
+        <v>-0.7568</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-4.9062</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.542</v>
+        <v>-0.8127</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2968</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8388</v>
+        <v>-0.7412</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2872</v>
+        <v>-2.0541</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3206</v>
+        <v>-0.7127</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9665</v>
+        <v>-1.3414</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0835</v>
+        <v>-0.9325</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1183</v>
+        <v>-0.1902</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2018</v>
+        <v>-0.7423</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9718</v>
+        <v>0.1289</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9869</v>
+        <v>0.0055</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9587</v>
+        <v>0.1234</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8883</v>
+        <v>-1.0614</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1315</v>
+        <v>-0.1956</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7568</v>
+        <v>-0.8657</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2644</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.9062</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3515</v>
+        <v>-0.6311</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1234</v>
+        <v>0.102</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4748</v>
+        <v>-0.733</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5267</v>
+        <v>-3.6823</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.2284</v>
+        <v>-4.6438</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7018</v>
+        <v>0.9616</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7228</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.596</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9406</v>
+        <v>-0.356</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6554</v>
+        <v>-0.3955</v>
       </c>
       <c r="V20" t="n">
         <v>1.2452</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4199000000000002</v>
+        <v>1.528700000000002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02010000000000023</v>
+        <v>0.02000000000000046</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4398999999999993</v>
+        <v>1.5089</v>
       </c>
       <c r="G21" t="n">
         <v>7.506099999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>8.694800000000001</v>
+        <v>8.694799999999999</v>
       </c>
       <c r="I21" t="n">
         <v>-1.1886</v>
@@ -2074,7 +2074,7 @@
         <v>1.2966</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9564</v>
+        <v>-3.956399999999999</v>
       </c>
       <c r="N21" t="n">
         <v>-1.4712</v>
@@ -2092,16 +2092,16 @@
         <v>14.1525</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.737299999999999</v>
+        <v>-3.7885</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2702</v>
+        <v>-1.2701</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.4671</v>
+        <v>-2.5183</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3017999999999996</v>
+        <v>-0.3017999999999998</v>
       </c>
       <c r="W21" t="n">
         <v>5.8672</v>
